--- a/reviews/a-envoyer/otea-filmakers-2026-10-05.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-10-05.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02T06:15:03</t>
+          <t>2026-10-02T10:58:11</t>
         </is>
       </c>
     </row>
